--- a/V513/ib_results_V513_ibbylayer.xlsx
+++ b/V513/ib_results_V513_ibbylayer.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interainc-my.sharepoint.com/personal/jwhite_intera_com/Documents/1d_csub/clay_thicknesses/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_085D78BFD3430E0E6235547658CC46F9A2358088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBE0464B-090A-4C8D-83D7-42A128AB4ECB}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_085D0AEF157C5E0F6235547658CC46F9A2358088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB328707-F2A7-4947-A666-5FD90CF06296}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -106,11 +105,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -421,13 +421,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="12" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -453,299 +446,299 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>4.1699768369148984</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>6.2409828858299997E-6</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>3.2853781524199999E-4</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>5.4242559411000001E-7</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="2">
         <v>2</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>8.7125088476348136</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>6.2409828858299997E-6</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>3.2853781524199999E-4</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <v>5.4242559411000001E-7</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="2">
         <v>3</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>11.935270247553129</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>6.2409828858299997E-6</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>3.2853781524199999E-4</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>5.4242559411000001E-7</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="2">
         <v>4</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>18.186898207458711</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>6.2409828858299997E-6</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>3.2853781524199999E-4</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>5.4242559411000001E-7</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="2">
         <v>5</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>23.090681291990851</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>6.2409828858299997E-6</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>3.2853781524199999E-4</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <v>5.4242559411000001E-7</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="2">
         <v>6</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>27.442501839489591</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>6.2409828858299997E-6</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>3.2853781524199999E-4</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <v>5.4242559411000001E-7</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="2">
         <v>7</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>42.689971448902071</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>6.2409828858299997E-6</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>3.2853781524199999E-4</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <v>5.4242559411000001E-7</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+      <c r="A9" s="4">
         <v>2</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>8</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>73.924522027659393</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>2.31182129048E-6</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>8.1841076888100004E-5</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <v>1.22931380203E-5</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>3</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>9</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>2.6194766610633708</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <v>4.8666660199399999E-6</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>2.0926192872500001E-4</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <v>1.9981980303700001E-7</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="2">
         <v>10</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>3.893539749786413</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>4.8666660199399999E-6</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>2.0926192872500001E-4</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <v>1.9981980303700001E-7</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="2">
         <v>11</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>6.2064513321257104</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <v>4.8666660199399999E-6</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <v>2.0926192872500001E-4</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
         <v>1.9981980303700001E-7</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="2">
         <v>12</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <v>5.9328161508192601</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <v>4.8666660199399999E-6</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>2.0926192872500001E-4</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="2">
         <v>1.9981980303700001E-7</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="2">
         <v>13</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <v>10.779767209970309</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <v>4.8666660199399999E-6</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <v>2.0926192872500001E-4</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="2">
         <v>1.9981980303700001E-7</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="2">
         <v>14</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="2">
         <v>23.066616740116139</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
         <v>4.8666660199399999E-6</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <v>2.0926192872500001E-4</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="2">
         <v>1.9981980303700001E-7</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="2">
         <v>15</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <v>37.06607492465568</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <v>4.8666660199399999E-6</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <v>2.0926192872500001E-4</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="2">
         <v>1.9981980303700001E-7</v>
       </c>
     </row>
